--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0001T0006Z000C1N76_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0001T0006Z000C1N76_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>31.13489259898555</v>
+        <v>5.059420047335152</v>
       </c>
       <c r="D2" t="n">
-        <v>32.34010682298506</v>
+        <v>5.255267358735073</v>
       </c>
       <c r="E2" t="n">
-        <v>7.741364811873932</v>
+        <v>1.257971781929514</v>
       </c>
       <c r="F2" t="n">
-        <v>7.753027356820738</v>
+        <v>1.25986694548337</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>12.55817689452459</v>
+        <v>2.040703745360247</v>
       </c>
       <c r="D3" t="n">
-        <v>13.38508879021923</v>
+        <v>2.175076928410625</v>
       </c>
       <c r="E3" t="n">
-        <v>7.741364811873932</v>
+        <v>1.257971781929514</v>
       </c>
       <c r="F3" t="n">
-        <v>7.753027356820738</v>
+        <v>1.25986694548337</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>25.1417595348484</v>
+        <v>4.085535924412866</v>
       </c>
       <c r="D4" t="n">
-        <v>23.87399185117136</v>
+        <v>3.879523675815346</v>
       </c>
       <c r="E4" t="n">
-        <v>7.741364811873932</v>
+        <v>1.257971781929514</v>
       </c>
       <c r="F4" t="n">
-        <v>7.753027356820738</v>
+        <v>1.25986694548337</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
